--- a/data/batches/B06_Findings_blank_populate/Test_Validation_Report/Test_Validation_Report_B06.xlsx
+++ b/data/batches/B06_Findings_blank_populate/Test_Validation_Report/Test_Validation_Report_B06.xlsx
@@ -1345,11 +1345,7 @@
           <t>SS</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>USUBJID</t>
